--- a/asx_eod_output/Report_XLSX/Report_20260911.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260911.xlsx
@@ -538,79 +538,79 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
+        <v>60.87</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>-2.57</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-4.05%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>57458</v>
+        <v>8000</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0</v>
+        <v>486960</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>-20560</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>60.87</v>
+        <v>0.005</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-2.57</v>
+        <v>0</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>8000</v>
+        <v>44090</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>486960</v>
+        <v>220.45</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-20560</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>CBA</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.005</v>
+        <v>154.19</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>44090</v>
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>220.45</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0</v>
@@ -619,109 +619,109 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CBA</t>
+          <t>CNB</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>154.19</v>
+        <v>0.945</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.99</v>
+        <v>-0.03</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0</v>
+        <v>9450</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CNB</t>
+          <t>CSL</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.945</v>
+        <v>167.1</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.03</v>
+        <v>-2.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9450</v>
+        <v>668400</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-300</v>
+        <v>-9600</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CSL</t>
+          <t>E25</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>167.1</v>
+        <v>0.275</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-2.4</v>
+        <v>0.005</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-1.42%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>668400</v>
+        <v>5500</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-9600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E25</t>
+          <t>EF2</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.275</v>
+        <v>19</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.005</v>
+        <v>-0.98</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>-4.90%</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>20000</v>
+        <v>3045</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5500</v>
+        <v>57855</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>100</v>
+        <v>-2984.1</v>
       </c>
     </row>
     <row r="13">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1672833.99</v>
+        <v>1730688.99</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>-36521.77</v>
+        <v>-39505.87</v>
       </c>
     </row>
   </sheetData>
